--- a/data/trans_orig/P57_AF_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2007</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>227214</t>
+          <t>230241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272259</t>
+          <t>272973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>237603</t>
+          <t>239224</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281201</t>
+          <t>282418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>479439</t>
+          <t>482807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>540600</t>
+          <t>539497</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220968</t>
+          <t>220254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266013</t>
+          <t>262986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>185071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229886</t>
+          <t>228265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>420116</t>
+          <t>421219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>481277</t>
+          <t>477909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>404615</t>
+          <t>402070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>458476</t>
+          <t>456843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>331161</t>
+          <t>332790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>380750</t>
+          <t>382613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>752762</t>
+          <t>752094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>822340</t>
+          <t>825152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277013</t>
+          <t>278646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330874</t>
+          <t>333419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243749</t>
+          <t>241886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293338</t>
+          <t>291709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>537648</t>
+          <t>534836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>607226</t>
+          <t>607894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362762</t>
+          <t>362766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>408993</t>
+          <t>413024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>381461</t>
+          <t>382985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>434189</t>
+          <t>436772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>763847</t>
+          <t>761488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>837432</t>
+          <t>832793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228590</t>
+          <t>224559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>274821</t>
+          <t>274817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254575</t>
+          <t>251992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307303</t>
+          <t>305779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488915</t>
+          <t>493554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>562500</t>
+          <t>564859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>299374</t>
+          <t>299947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345629</t>
+          <t>346834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292940</t>
+          <t>295734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>336708</t>
+          <t>338915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>608724</t>
+          <t>608478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>673976</t>
+          <t>671743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173518</t>
+          <t>172313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219773</t>
+          <t>219200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178934</t>
+          <t>176727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>222702</t>
+          <t>219908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360813</t>
+          <t>363046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>426065</t>
+          <t>426311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>228327</t>
+          <t>229308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>264935</t>
+          <t>266763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>249673</t>
+          <t>248999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286558</t>
+          <t>286759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>489995</t>
+          <t>485766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>542055</t>
+          <t>544224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120931</t>
+          <t>119103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157539</t>
+          <t>156558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117428</t>
+          <t>117227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154313</t>
+          <t>154987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247797</t>
+          <t>245628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299857</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>181057</t>
+          <t>180483</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>212266</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>204712</t>
+          <t>203428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>237428</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>393862</t>
+          <t>393901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>441979</t>
+          <t>437599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>78970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109775</t>
+          <t>110349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105506</t>
+          <t>104870</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>138222</t>
+          <t>139506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>191787</t>
+          <t>196167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239904</t>
+          <t>239865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137926</t>
+          <t>138661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162804</t>
+          <t>163926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>213708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250629</t>
+          <t>249374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>362741</t>
+          <t>361940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407059</t>
+          <t>408250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>45957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71957</t>
+          <t>71222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83279</t>
+          <t>84534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119766</t>
+          <t>120200</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136732</t>
+          <t>135541</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>181050</t>
+          <t>181851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1935520</t>
+          <t>1931499</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2047449</t>
+          <t>2040308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2009712</t>
+          <t>2014386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2120774</t>
+          <t>2124563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3977174</t>
+          <t>3970701</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4128712</t>
+          <t>4129880</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1224577</t>
+          <t>1231718</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1336506</t>
+          <t>1340527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1256448</t>
+          <t>1252659</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1367510</t>
+          <t>1362836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2520536</t>
+          <t>2519368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2672074</t>
+          <t>2678547</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2012</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2012 (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>227746</t>
+          <t>229058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272723</t>
+          <t>273821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>224016</t>
+          <t>223984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>266048</t>
+          <t>263236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>464476</t>
+          <t>464798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524604</t>
+          <t>524912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>178423</t>
+          <t>177325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223400</t>
+          <t>222088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163209</t>
+          <t>166021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205241</t>
+          <t>205273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355799</t>
+          <t>355491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415927</t>
+          <t>415605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>366024</t>
+          <t>367281</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>421413</t>
+          <t>420426</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>375707</t>
+          <t>374978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>421406</t>
+          <t>422544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>753336</t>
+          <t>757690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>824828</t>
+          <t>828778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>261604</t>
+          <t>262591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>316993</t>
+          <t>315736</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>186697</t>
+          <t>185559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232396</t>
+          <t>233125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466292</t>
+          <t>462342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>537784</t>
+          <t>533430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>418727</t>
+          <t>418650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>469526</t>
+          <t>471389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>436273</t>
+          <t>432637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488157</t>
+          <t>487499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>870479</t>
+          <t>867199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>941884</t>
+          <t>942163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>211147</t>
+          <t>209284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261946</t>
+          <t>262023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218380</t>
+          <t>219038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270264</t>
+          <t>273900</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445326</t>
+          <t>445047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>516731</t>
+          <t>520011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>363222</t>
+          <t>363267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>411968</t>
+          <t>412740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>420115</t>
+          <t>420418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>465760</t>
+          <t>464889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>796188</t>
+          <t>795247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>864352</t>
+          <t>864317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198634</t>
+          <t>197862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>247380</t>
+          <t>247335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145581</t>
+          <t>146452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191226</t>
+          <t>190923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357591</t>
+          <t>357626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>425755</t>
+          <t>426696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230017</t>
+          <t>231292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>273116</t>
+          <t>274250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285258</t>
+          <t>285142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>324755</t>
+          <t>326848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>531012</t>
+          <t>528470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>588632</t>
+          <t>587183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154282</t>
+          <t>153148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197381</t>
+          <t>196106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119968</t>
+          <t>117875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159465</t>
+          <t>159581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283489</t>
+          <t>284938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341109</t>
+          <t>343651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>188181</t>
+          <t>186974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220302</t>
+          <t>220305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227340</t>
+          <t>226543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261324</t>
+          <t>261558</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>423328</t>
+          <t>424215</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>472764</t>
+          <t>472300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84798</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116919</t>
+          <t>118126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87146</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121130</t>
+          <t>121927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180807</t>
+          <t>181271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>230243</t>
+          <t>229356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159226</t>
+          <t>160766</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190073</t>
+          <t>191072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>239817</t>
+          <t>241756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>279716</t>
+          <t>279711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>411782</t>
+          <t>406797</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>458631</t>
+          <t>458207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57744</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88591</t>
+          <t>87051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103840</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143739</t>
+          <t>141800</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>172742</t>
+          <t>173166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>224576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2047014</t>
+          <t>2049151</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2164819</t>
+          <t>2166148</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2303002</t>
+          <t>2300373</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2419673</t>
+          <t>2417984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4389377</t>
+          <t>4388709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4546755</t>
+          <t>4554484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1240934</t>
+          <t>1239605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1358739</t>
+          <t>1356602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1112315</t>
+          <t>1114004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1228986</t>
+          <t>1231615</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2390986</t>
+          <t>2383257</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2548364</t>
+          <t>2549032</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2016</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>271482</t>
+          <t>272094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>309510</t>
+          <t>312374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251231</t>
+          <t>252371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289386</t>
+          <t>288286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>535398</t>
+          <t>535256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>589658</t>
+          <t>590188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109953</t>
+          <t>107089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147981</t>
+          <t>147369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106369</t>
+          <t>107469</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144524</t>
+          <t>143384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225560</t>
+          <t>225030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279820</t>
+          <t>279962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>420181</t>
+          <t>420691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>462753</t>
+          <t>460924</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>388866</t>
+          <t>392510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>431990</t>
+          <t>431851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>823471</t>
+          <t>823660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>882673</t>
+          <t>881670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>124349</t>
+          <t>126178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166921</t>
+          <t>166411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128156</t>
+          <t>128295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171280</t>
+          <t>167636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264575</t>
+          <t>265578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323777</t>
+          <t>323588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>464573</t>
+          <t>465992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>511563</t>
+          <t>511650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>451268</t>
+          <t>450022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>496671</t>
+          <t>495751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>932585</t>
+          <t>932402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>996907</t>
+          <t>997037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156668</t>
+          <t>156581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203658</t>
+          <t>202239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156419</t>
+          <t>157339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201822</t>
+          <t>203068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324415</t>
+          <t>324285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>388737</t>
+          <t>388920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>464331</t>
+          <t>466063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>509493</t>
+          <t>509102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>477351</t>
+          <t>479038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>522237</t>
+          <t>522146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>960902</t>
+          <t>956676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1023488</t>
+          <t>1017767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132702</t>
+          <t>133093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177864</t>
+          <t>176132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>126931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171726</t>
+          <t>170039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>267784</t>
+          <t>273505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330370</t>
+          <t>334596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>326095</t>
+          <t>325474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>365896</t>
+          <t>366450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>366693</t>
+          <t>365791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>403848</t>
+          <t>405076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>703402</t>
+          <t>702982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>758217</t>
+          <t>759215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106620</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146421</t>
+          <t>147042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89674</t>
+          <t>88446</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>127731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207821</t>
+          <t>206823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262636</t>
+          <t>263056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>221544</t>
+          <t>221973</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>255007</t>
+          <t>254767</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>286051</t>
+          <t>287356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>318833</t>
+          <t>316744</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>516904</t>
+          <t>518953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>561684</t>
+          <t>565839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78377</t>
+          <t>78617</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111840</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90738</t>
+          <t>89433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148489</t>
+          <t>144334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193269</t>
+          <t>191220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187526</t>
+          <t>187017</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210991</t>
+          <t>210743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>314831</t>
+          <t>315741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>348747</t>
+          <t>349225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>511078</t>
+          <t>509702</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>552334</t>
+          <t>551865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45142</t>
+          <t>45390</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68607</t>
+          <t>69116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48775</t>
+          <t>48297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82691</t>
+          <t>81781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101321</t>
+          <t>101790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>142577</t>
+          <t>143953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2443440</t>
+          <t>2446255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2549433</t>
+          <t>2549832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2628925</t>
+          <t>2632941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2732085</t>
+          <t>2732581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5110015</t>
+          <t>5108940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5256477</t>
+          <t>5254090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>829591</t>
+          <t>829192</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>935584</t>
+          <t>932769</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>793816</t>
+          <t>793320</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>896976</t>
+          <t>892960</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1648449</t>
+          <t>1650836</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1794911</t>
+          <t>1795986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2023</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2023 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111328</t>
+          <t>112021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174956</t>
+          <t>177846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110221</t>
+          <t>113699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158012</t>
+          <t>159037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242289</t>
+          <t>238602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>319296</t>
+          <t>323383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223375</t>
+          <t>220485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287003</t>
+          <t>286310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155188</t>
+          <t>154163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202979</t>
+          <t>199501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>392235</t>
+          <t>388148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469242</t>
+          <t>472929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195111</t>
+          <t>198116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251633</t>
+          <t>250898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126203</t>
+          <t>129234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252965</t>
+          <t>249224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315338</t>
+          <t>329250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>483953</t>
+          <t>484159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170571</t>
+          <t>171306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227093</t>
+          <t>224088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257440</t>
+          <t>261181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>384202</t>
+          <t>381171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448656</t>
+          <t>448450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>617271</t>
+          <t>603359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>274542</t>
+          <t>275492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323889</t>
+          <t>323617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>275722</t>
+          <t>274966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>315311</t>
+          <t>313939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565706</t>
+          <t>565942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>626055</t>
+          <t>624922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208610</t>
+          <t>208882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257957</t>
+          <t>257007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225788</t>
+          <t>227160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>265377</t>
+          <t>266133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447542</t>
+          <t>448675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507891</t>
+          <t>507655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163788</t>
+          <t>167703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>507649</t>
+          <t>509005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>328631</t>
+          <t>327396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>421339</t>
+          <t>420064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441213</t>
+          <t>472505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>906605</t>
+          <t>909860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371822</t>
+          <t>370466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>715683</t>
+          <t>711768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283431</t>
+          <t>284706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376139</t>
+          <t>377374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677636</t>
+          <t>674381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1143028</t>
+          <t>1111736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>320285</t>
+          <t>318126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>363516</t>
+          <t>363027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>325832</t>
+          <t>327747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>358475</t>
+          <t>360564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>657050</t>
+          <t>657460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>712775</t>
+          <t>712835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193282</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>236513</t>
+          <t>238672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181482</t>
+          <t>179393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214125</t>
+          <t>212210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383980</t>
+          <t>383920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439705</t>
+          <t>439295</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211686</t>
+          <t>213060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>243292</t>
+          <t>243566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>362341</t>
+          <t>359178</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>543836</t>
+          <t>543019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>587502</t>
+          <t>591775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>813852</t>
+          <t>809327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123720</t>
+          <t>123446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155326</t>
+          <t>153952</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61351</t>
+          <t>62168</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242846</t>
+          <t>246009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158347</t>
+          <t>162872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384697</t>
+          <t>380424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174243</t>
+          <t>173434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197755</t>
+          <t>199039</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>279013</t>
+          <t>279066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>303854</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>457800</t>
+          <t>458166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>497643</t>
+          <t>495736</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79467</t>
+          <t>78183</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>102979</t>
+          <t>103788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111050</t>
+          <t>110566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135891</t>
+          <t>135838</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>194483</t>
+          <t>196390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>234326</t>
+          <t>233960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1347645</t>
+          <t>1388323</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1940319</t>
+          <t>1943104</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1982363</t>
+          <t>1978061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2366368</t>
+          <t>2390665</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3491972</t>
+          <t>3491842</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4156024</t>
+          <t>4185170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1493217</t>
+          <t>1490432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2085891</t>
+          <t>2045213</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1263154</t>
+          <t>1238857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1647159</t>
+          <t>1651461</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2907034</t>
+          <t>2877888</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3571086</t>
+          <t>3571216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P57_AF_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>230241</t>
+          <t>230286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272973</t>
+          <t>273628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>239224</t>
+          <t>238057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>280564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>482807</t>
+          <t>484460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>539497</t>
+          <t>543208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220254</t>
+          <t>219599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262986</t>
+          <t>262941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185071</t>
+          <t>186925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228265</t>
+          <t>229432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>421219</t>
+          <t>417508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477909</t>
+          <t>476256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>402070</t>
+          <t>403975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>456843</t>
+          <t>458579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>332790</t>
+          <t>332326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>382613</t>
+          <t>381674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>752094</t>
+          <t>748829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>825152</t>
+          <t>822110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278646</t>
+          <t>276910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333419</t>
+          <t>331514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241886</t>
+          <t>242825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291709</t>
+          <t>292173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>534836</t>
+          <t>537878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>607894</t>
+          <t>611159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362766</t>
+          <t>361909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>413024</t>
+          <t>413087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>382985</t>
+          <t>386781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>436772</t>
+          <t>438157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>761488</t>
+          <t>759334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>832793</t>
+          <t>832937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>224559</t>
+          <t>224496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>274817</t>
+          <t>275674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251992</t>
+          <t>250607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305779</t>
+          <t>301983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>493554</t>
+          <t>493410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564859</t>
+          <t>567013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>299947</t>
+          <t>299193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>346834</t>
+          <t>346550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295734</t>
+          <t>293477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>338915</t>
+          <t>340199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>608478</t>
+          <t>607405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>671743</t>
+          <t>673818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172313</t>
+          <t>172597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219200</t>
+          <t>219954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176727</t>
+          <t>175443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219908</t>
+          <t>222165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363046</t>
+          <t>360971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>426311</t>
+          <t>427384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229308</t>
+          <t>228494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266763</t>
+          <t>265417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>248999</t>
+          <t>248301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286759</t>
+          <t>285882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>485766</t>
+          <t>488967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>544224</t>
+          <t>541167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119103</t>
+          <t>120449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156558</t>
+          <t>157372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117227</t>
+          <t>118104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154987</t>
+          <t>155685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245628</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>300885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>180483</t>
+          <t>180172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>211862</t>
+          <t>210951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203428</t>
+          <t>204035</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>238064</t>
+          <t>238463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>393901</t>
+          <t>392784</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>437599</t>
+          <t>438571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78970</t>
+          <t>79881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110349</t>
+          <t>110660</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104870</t>
+          <t>104471</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>139506</t>
+          <t>138899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196167</t>
+          <t>195195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239865</t>
+          <t>240982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138661</t>
+          <t>138208</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163926</t>
+          <t>163552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>213708</t>
+          <t>216301</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249374</t>
+          <t>251648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>361940</t>
+          <t>362326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408250</t>
+          <t>405602</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45957</t>
+          <t>46331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71222</t>
+          <t>71675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>82260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120200</t>
+          <t>117607</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>135541</t>
+          <t>138189</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>181851</t>
+          <t>181465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1931499</t>
+          <t>1929022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2040308</t>
+          <t>2039205</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2014386</t>
+          <t>2014582</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2124563</t>
+          <t>2123827</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3970701</t>
+          <t>3973465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4129880</t>
+          <t>4136987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1231718</t>
+          <t>1232821</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1340527</t>
+          <t>1343004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1252659</t>
+          <t>1253395</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1362836</t>
+          <t>1362640</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2519368</t>
+          <t>2512261</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2678547</t>
+          <t>2675783</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>229058</t>
+          <t>229305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273821</t>
+          <t>272883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223984</t>
+          <t>223543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>263236</t>
+          <t>264479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>464798</t>
+          <t>465338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524912</t>
+          <t>525524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>177325</t>
+          <t>178263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222088</t>
+          <t>221841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166021</t>
+          <t>164778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205273</t>
+          <t>205714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355491</t>
+          <t>354879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415605</t>
+          <t>415065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367281</t>
+          <t>365007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>420426</t>
+          <t>418668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>374978</t>
+          <t>374829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>422544</t>
+          <t>423679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>757690</t>
+          <t>757283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>828778</t>
+          <t>830383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262591</t>
+          <t>264349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>315736</t>
+          <t>318010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185559</t>
+          <t>184424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233125</t>
+          <t>233274</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462342</t>
+          <t>460737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>533430</t>
+          <t>533837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>418650</t>
+          <t>417454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>471389</t>
+          <t>469165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>432637</t>
+          <t>434439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>487499</t>
+          <t>489082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>867199</t>
+          <t>869451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>942163</t>
+          <t>940877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209284</t>
+          <t>211508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262023</t>
+          <t>263219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219038</t>
+          <t>217455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273900</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445047</t>
+          <t>446333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>520011</t>
+          <t>517759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>363267</t>
+          <t>361856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>412740</t>
+          <t>412042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>420418</t>
+          <t>419103</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>464889</t>
+          <t>464724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>795247</t>
+          <t>800087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>864317</t>
+          <t>868752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197862</t>
+          <t>198560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>247335</t>
+          <t>248746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146452</t>
+          <t>146617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190923</t>
+          <t>192238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357626</t>
+          <t>353191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>426696</t>
+          <t>421856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>231292</t>
+          <t>232928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274250</t>
+          <t>274139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285142</t>
+          <t>286455</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>326848</t>
+          <t>326559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>528470</t>
+          <t>530191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>587183</t>
+          <t>588633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153148</t>
+          <t>153259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196106</t>
+          <t>194470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117875</t>
+          <t>118164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159581</t>
+          <t>158268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284938</t>
+          <t>283488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343651</t>
+          <t>341930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>186974</t>
+          <t>186926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220305</t>
+          <t>220133</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>226543</t>
+          <t>228168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261558</t>
+          <t>262220</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>424215</t>
+          <t>423303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>472300</t>
+          <t>472296</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84795</t>
+          <t>84967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118126</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>86250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121927</t>
+          <t>120302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>181271</t>
+          <t>181275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229356</t>
+          <t>230268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160766</t>
+          <t>158629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191072</t>
+          <t>189567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>241756</t>
+          <t>240363</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>279711</t>
+          <t>276505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>406797</t>
+          <t>410999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>458207</t>
+          <t>459089</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56745</t>
+          <t>58250</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87051</t>
+          <t>89188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>107051</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141800</t>
+          <t>143193</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>173166</t>
+          <t>172284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>224576</t>
+          <t>220374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2049151</t>
+          <t>2056241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2166148</t>
+          <t>2169055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2300373</t>
+          <t>2301178</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2417984</t>
+          <t>2417346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4388709</t>
+          <t>4383012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4554484</t>
+          <t>4554313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1239605</t>
+          <t>1236698</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1356602</t>
+          <t>1349512</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1114004</t>
+          <t>1114642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1231615</t>
+          <t>1230810</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2383257</t>
+          <t>2383428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2549032</t>
+          <t>2554729</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272094</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>312374</t>
+          <t>312077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252371</t>
+          <t>256367</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288286</t>
+          <t>288997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>535256</t>
+          <t>535252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>590188</t>
+          <t>587988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107089</t>
+          <t>107386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147369</t>
+          <t>145401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107469</t>
+          <t>106758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143384</t>
+          <t>139388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225030</t>
+          <t>227230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279962</t>
+          <t>279966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>420691</t>
+          <t>419721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>460924</t>
+          <t>461662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>392510</t>
+          <t>389102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>431851</t>
+          <t>431312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>823660</t>
+          <t>823880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>881670</t>
+          <t>881636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126178</t>
+          <t>125440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166411</t>
+          <t>167381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128295</t>
+          <t>128834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167636</t>
+          <t>171044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265578</t>
+          <t>265612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323588</t>
+          <t>323368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>465992</t>
+          <t>465959</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>511650</t>
+          <t>512423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>450022</t>
+          <t>449035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>495751</t>
+          <t>497108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>932402</t>
+          <t>932127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>997037</t>
+          <t>996341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156581</t>
+          <t>155808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202239</t>
+          <t>202272</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157339</t>
+          <t>155982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>203068</t>
+          <t>204055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324285</t>
+          <t>324981</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>388920</t>
+          <t>389195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>466063</t>
+          <t>466021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>509102</t>
+          <t>512276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>479038</t>
+          <t>476806</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>522146</t>
+          <t>520444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>956676</t>
+          <t>958787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1017767</t>
+          <t>1020951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133093</t>
+          <t>129919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176132</t>
+          <t>176174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126931</t>
+          <t>128633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170039</t>
+          <t>172271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273505</t>
+          <t>270321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334596</t>
+          <t>332485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>325474</t>
+          <t>326058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>366450</t>
+          <t>366785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>365791</t>
+          <t>364806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>405076</t>
+          <t>404318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702982</t>
+          <t>703630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>759215</t>
+          <t>762405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106066</t>
+          <t>105731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147042</t>
+          <t>146458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88446</t>
+          <t>89204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127731</t>
+          <t>128716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>206823</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263056</t>
+          <t>262408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>221973</t>
+          <t>221679</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>254767</t>
+          <t>256412</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>287356</t>
+          <t>285590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316744</t>
+          <t>318523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>518953</t>
+          <t>519917</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>565839</t>
+          <t>564545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78617</t>
+          <t>76972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111411</t>
+          <t>111705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>58266</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89433</t>
+          <t>91199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144334</t>
+          <t>145628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191220</t>
+          <t>190256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187017</t>
+          <t>187291</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210743</t>
+          <t>212015</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>315741</t>
+          <t>314267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>349225</t>
+          <t>349729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>509702</t>
+          <t>510889</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>551865</t>
+          <t>552711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45390</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>68842</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48297</t>
+          <t>47793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>83255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101790</t>
+          <t>100944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>143953</t>
+          <t>142766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2446255</t>
+          <t>2444893</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2549832</t>
+          <t>2550717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2632941</t>
+          <t>2627909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2732581</t>
+          <t>2732923</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5108940</t>
+          <t>5114418</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5254090</t>
+          <t>5252865</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>829192</t>
+          <t>828307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>932769</t>
+          <t>934131</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>793320</t>
+          <t>792978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>892960</t>
+          <t>897992</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1650836</t>
+          <t>1652061</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1795986</t>
+          <t>1790508</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>142713</t>
+          <t>155363</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112021</t>
+          <t>125685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177846</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>135451</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113699</t>
+          <t>139907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159037</t>
+          <t>190659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>278164</t>
+          <t>321865</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>238602</t>
+          <t>284159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>323383</t>
+          <t>363845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>255618</t>
+          <t>250586</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220485</t>
+          <t>218173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286310</t>
+          <t>280264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>177749</t>
+          <t>196010</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154163</t>
+          <t>171853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199501</t>
+          <t>222605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>433367</t>
+          <t>446596</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388148</t>
+          <t>404616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>472929</t>
+          <t>484302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>398331</t>
+          <t>405949</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>398331</t>
+          <t>405949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>398331</t>
+          <t>405949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>711531</t>
+          <t>768461</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>711531</t>
+          <t>768461</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>711531</t>
+          <t>768461</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>225736</t>
+          <t>260916</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>198116</t>
+          <t>233627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250898</t>
+          <t>290063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>209296</t>
+          <t>246219</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>129234</t>
+          <t>222443</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249224</t>
+          <t>271677</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>435031</t>
+          <t>507136</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329250</t>
+          <t>472572</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484159</t>
+          <t>544835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>196468</t>
+          <t>214640</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171306</t>
+          <t>185493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224088</t>
+          <t>241929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>301109</t>
+          <t>252898</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261181</t>
+          <t>227440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>381171</t>
+          <t>276674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>497578</t>
+          <t>467537</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448450</t>
+          <t>429838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>603359</t>
+          <t>502101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422204</t>
+          <t>475556</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422204</t>
+          <t>475556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422204</t>
+          <t>475556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510405</t>
+          <t>499117</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510405</t>
+          <t>499117</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510405</t>
+          <t>499117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>932609</t>
+          <t>974673</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>932609</t>
+          <t>974673</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>932609</t>
+          <t>974673</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>299598</t>
+          <t>354899</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>275492</t>
+          <t>326870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323617</t>
+          <t>381044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>295351</t>
+          <t>345932</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>274966</t>
+          <t>326107</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>313939</t>
+          <t>366105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>594949</t>
+          <t>700831</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565942</t>
+          <t>665938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>624922</t>
+          <t>732607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>232901</t>
+          <t>259450</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208882</t>
+          <t>233305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257007</t>
+          <t>287479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>245748</t>
+          <t>274820</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227160</t>
+          <t>254647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266133</t>
+          <t>294645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>478648</t>
+          <t>534270</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>448675</t>
+          <t>502494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507655</t>
+          <t>569163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>532499</t>
+          <t>614349</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>532499</t>
+          <t>614349</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>532499</t>
+          <t>614349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541099</t>
+          <t>620752</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541099</t>
+          <t>620752</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541099</t>
+          <t>620752</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1073597</t>
+          <t>1235101</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1073597</t>
+          <t>1235101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073597</t>
+          <t>1235101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>357146</t>
+          <t>392540</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167703</t>
+          <t>367379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>509005</t>
+          <t>421078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>393249</t>
+          <t>429232</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>327396</t>
+          <t>409600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>420064</t>
+          <t>450857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>750395</t>
+          <t>821773</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>472505</t>
+          <t>786192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>909860</t>
+          <t>854569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>522325</t>
+          <t>299698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>370466</t>
+          <t>271160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>711768</t>
+          <t>324859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>311521</t>
+          <t>298551</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284706</t>
+          <t>276926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>377374</t>
+          <t>318183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>833846</t>
+          <t>598248</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674381</t>
+          <t>565452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1111736</t>
+          <t>633829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>879471</t>
+          <t>692238</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>879471</t>
+          <t>692238</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>879471</t>
+          <t>692238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>704770</t>
+          <t>727783</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>704770</t>
+          <t>727783</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>704770</t>
+          <t>727783</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1584241</t>
+          <t>1420021</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1584241</t>
+          <t>1420021</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1584241</t>
+          <t>1420021</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>342500</t>
+          <t>375846</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>318126</t>
+          <t>354958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>363027</t>
+          <t>402905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>342915</t>
+          <t>379377</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>327747</t>
+          <t>359056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>360564</t>
+          <t>396086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>685415</t>
+          <t>755224</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>657460</t>
+          <t>726417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>712835</t>
+          <t>786650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>214298</t>
+          <t>229213</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193771</t>
+          <t>202154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238672</t>
+          <t>250101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>197042</t>
+          <t>220208</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179393</t>
+          <t>203499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212210</t>
+          <t>240529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>411340</t>
+          <t>449420</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383920</t>
+          <t>417994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439295</t>
+          <t>478227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>556798</t>
+          <t>605059</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>556798</t>
+          <t>605059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>556798</t>
+          <t>605059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>539957</t>
+          <t>599585</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>539957</t>
+          <t>599585</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>539957</t>
+          <t>599585</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1096755</t>
+          <t>1204644</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1096755</t>
+          <t>1204644</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1096755</t>
+          <t>1204644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>227592</t>
+          <t>252378</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213060</t>
+          <t>235799</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>243566</t>
+          <t>268710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>448114</t>
+          <t>266024</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>359178</t>
+          <t>249671</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>543019</t>
+          <t>279433</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>675706</t>
+          <t>518402</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>591775</t>
+          <t>496263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>809327</t>
+          <t>540109</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>139420</t>
+          <t>153585</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123446</t>
+          <t>137253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153952</t>
+          <t>170164</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>157073</t>
+          <t>169792</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62168</t>
+          <t>156383</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246009</t>
+          <t>186145</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>296493</t>
+          <t>323377</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>162872</t>
+          <t>301670</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>380424</t>
+          <t>345516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367012</t>
+          <t>405963</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367012</t>
+          <t>405963</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367012</t>
+          <t>405963</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>605187</t>
+          <t>435816</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>605187</t>
+          <t>435816</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>605187</t>
+          <t>435816</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>972199</t>
+          <t>841779</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>972199</t>
+          <t>841779</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>972199</t>
+          <t>841779</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,22 +11723,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>186492</t>
+          <t>205092</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173434</t>
+          <t>190499</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199039</t>
+          <t>218043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>292414</t>
+          <t>318874</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>279066</t>
+          <t>303977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>334186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>478906</t>
+          <t>523967</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>458166</t>
+          <t>503653</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>495736</t>
+          <t>543481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -11836,27 +11836,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>90730</t>
+          <t>99437</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78183</t>
+          <t>86486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103788</t>
+          <t>114030</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>122490</t>
+          <t>134120</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110566</t>
+          <t>118808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135838</t>
+          <t>149017</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>213220</t>
+          <t>233556</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>196390</t>
+          <t>214042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233960</t>
+          <t>253870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>277222</t>
+          <t>304529</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>277222</t>
+          <t>304529</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>277222</t>
+          <t>304529</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>414904</t>
+          <t>452994</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>414904</t>
+          <t>452994</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>414904</t>
+          <t>452994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>692126</t>
+          <t>757523</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>692126</t>
+          <t>757523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>692126</t>
+          <t>757523</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1781775</t>
+          <t>1997035</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1388323</t>
+          <t>1925935</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1943104</t>
+          <t>2061694</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2116789</t>
+          <t>2152162</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1978061</t>
+          <t>2093941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2390665</t>
+          <t>2208051</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3898565</t>
+          <t>4149198</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3491842</t>
+          <t>4062573</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4185170</t>
+          <t>4237959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1651761</t>
+          <t>1506608</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1490432</t>
+          <t>1441949</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2045213</t>
+          <t>1577708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1512733</t>
+          <t>1546398</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1238857</t>
+          <t>1490509</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1651461</t>
+          <t>1604619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3164493</t>
+          <t>3053005</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2877888</t>
+          <t>2964244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3571216</t>
+          <t>3139630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
